--- a/server/templates/Template Excel Presupuesto.xlsx
+++ b/server/templates/Template Excel Presupuesto.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w.pallero.gomez\Desktop\Onyria\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w.pallero.gomez\Desktop\onyria-presupuestos\onyria-presupuestos\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E1CB23-B2EC-4E5B-9FC8-263FDEB5ADAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3B1312-0F5E-466B-BA76-0A4AA7FD4727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -724,7 +724,7 @@
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -746,9 +746,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -935,33 +932,6 @@
     <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -972,6 +942,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1208,7 +1205,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>437400</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>58634</xdr:rowOff>
+      <xdr:rowOff>58633</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1439,32 +1436,32 @@
     <col min="13" max="13" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="4"/>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="112" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
+      <c r="A3" s="102" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="113" t="s">
+      <c r="G3" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="113"/>
-      <c r="L3" s="113"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -1480,707 +1477,702 @@
         <v>5</v>
       </c>
       <c r="E4" s="9"/>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12">
-        <v>1</v>
-      </c>
-      <c r="J4" s="13">
+      <c r="H4" s="10"/>
+      <c r="I4" s="11">
+        <f>SUM(C28:C36)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
         <f>E39</f>
         <v>0</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17">
-        <v>0</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="B5" s="15"/>
+      <c r="C5" s="16">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15">
         <f t="shared" ref="D5:D10" si="0">C5*B5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="G5" s="19" t="s">
+      <c r="E5" s="17"/>
+      <c r="G5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="12">
-        <v>1</v>
-      </c>
-      <c r="J5" s="13">
+      <c r="H5" s="19"/>
+      <c r="I5" s="11">
+        <f>SUM(C43:C51)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
         <f>D54</f>
         <v>0</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17">
-        <v>0</v>
-      </c>
-      <c r="D6" s="16">
+      <c r="B6" s="15"/>
+      <c r="C6" s="16">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E6" s="21"/>
-      <c r="G6" s="19" t="s">
+      <c r="E6" s="20"/>
+      <c r="G6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="12">
-        <v>1</v>
-      </c>
-      <c r="J6" s="13">
+      <c r="H6" s="19"/>
+      <c r="I6" s="11">
+        <f>SUM(C59:C65)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
         <f>D66</f>
         <v>0</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="17">
-        <v>0</v>
-      </c>
-      <c r="D7" s="16">
+      <c r="B7" s="21"/>
+      <c r="C7" s="16">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E7" s="21"/>
-      <c r="G7" s="19" t="s">
+      <c r="E7" s="20"/>
+      <c r="G7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="12">
-        <v>1</v>
-      </c>
-      <c r="J7" s="13">
+      <c r="H7" s="19"/>
+      <c r="I7" s="11">
+        <f>SUM(I27:I35)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="12">
         <f>K36*I7</f>
         <v>0</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="17">
-        <v>0</v>
-      </c>
-      <c r="D8" s="16">
+      <c r="B8" s="21"/>
+      <c r="C8" s="16">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="G8" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" s="20"/>
-      <c r="I8" s="12">
-        <v>1</v>
-      </c>
-      <c r="J8" s="13">
+      <c r="E8" s="22"/>
+      <c r="G8" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="11">
+        <f>SUM(C5:C18)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="12">
         <f>D21*I8</f>
         <v>0</v>
       </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="17">
-        <v>0</v>
-      </c>
-      <c r="D9" s="16">
+      <c r="B9" s="21"/>
+      <c r="C9" s="16">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E9" s="21"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="E9" s="20"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
     </row>
     <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="17">
-        <v>0</v>
-      </c>
-      <c r="D10" s="16">
+      <c r="B10" s="21"/>
+      <c r="C10" s="16">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="21"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
+      <c r="E10" s="20"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="17">
-        <v>0</v>
-      </c>
-      <c r="D11" s="16">
+      <c r="B11" s="21"/>
+      <c r="C11" s="16">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15">
         <f t="shared" ref="D11:D18" si="1">B11*C11</f>
         <v>0</v>
       </c>
-      <c r="E11" s="21"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+      <c r="E11" s="20"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="17">
-        <v>0</v>
-      </c>
-      <c r="D12" s="16">
+      <c r="B12" s="21"/>
+      <c r="C12" s="16">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="G12" s="114" t="s">
+      <c r="E12" s="20"/>
+      <c r="G12" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="114"/>
-      <c r="I12" s="28">
+      <c r="H12" s="104"/>
+      <c r="I12" s="27">
         <f>SUM(B13:I13)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="29">
+      <c r="J12" s="28">
         <f>SUM(J4:J11)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="17">
-        <v>0</v>
-      </c>
-      <c r="D13" s="16">
+      <c r="B13" s="21"/>
+      <c r="C13" s="16">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E13" s="21"/>
-      <c r="G13" s="110" t="s">
+      <c r="E13" s="20"/>
+      <c r="G13" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="110"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="31"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="30"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="17">
-        <v>0</v>
-      </c>
-      <c r="D14" s="16">
+      <c r="B14" s="21"/>
+      <c r="C14" s="16">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="G14" s="110" t="s">
+      <c r="E14" s="20"/>
+      <c r="G14" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="110"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="32">
+      <c r="H14" s="105"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="31">
         <f>J15-J13</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="17">
-        <v>0</v>
-      </c>
-      <c r="D15" s="16">
+      <c r="A15" s="14"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="16">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="G15" s="110" t="s">
+      <c r="E15" s="20"/>
+      <c r="G15" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="110"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="32">
+      <c r="H15" s="105"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="31">
         <f>J13*1.19</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="17">
-        <v>0</v>
-      </c>
-      <c r="D16" s="16">
+      <c r="A16" s="14"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="16">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="17">
-        <v>0</v>
-      </c>
-      <c r="D17" s="16">
+      <c r="A17" s="32"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="16">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E17" s="21"/>
-      <c r="J17" s="34"/>
+      <c r="E17" s="20"/>
+      <c r="J17" s="33"/>
     </row>
     <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="17">
-        <v>0</v>
-      </c>
-      <c r="D18" s="16">
+      <c r="A18" s="34"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="16">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E18" s="21"/>
-      <c r="J18" s="36"/>
+      <c r="E18" s="20"/>
+      <c r="J18" s="35"/>
     </row>
     <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="108"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="37">
+      <c r="B19" s="106"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="36">
         <f>SUM(D5:D18)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="38"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="40"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
+      <c r="E19" s="37"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="39"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="104"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="37">
+      <c r="B20" s="107"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="36">
         <f>D19*B20/100</f>
         <v>0</v>
       </c>
-      <c r="G20" s="36"/>
-      <c r="H20" s="41"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="40"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="109" t="s">
+      <c r="A21" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="109"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="42">
+      <c r="B21" s="108"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="41">
         <f>D19-D20</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="J23" s="43"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G25" s="107" t="s">
+      <c r="G25" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="107"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="107"/>
-      <c r="K25" s="107"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="109"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="107" t="s">
+      <c r="A26" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="107"/>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
-      <c r="G26" s="44" t="s">
+      <c r="B26" s="109"/>
+      <c r="C26" s="109"/>
+      <c r="D26" s="109"/>
+      <c r="E26" s="109"/>
+      <c r="G26" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="45" t="s">
+      <c r="H26" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="I26" s="45" t="s">
+      <c r="I26" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45" t="s">
+      <c r="J26" s="44"/>
+      <c r="K26" s="44" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="45" t="s">
+      <c r="C27" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45" t="s">
+      <c r="D27" s="44"/>
+      <c r="E27" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="G27" s="46" t="s">
+      <c r="G27" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="47">
-        <v>10000</v>
-      </c>
-      <c r="I27" s="48">
-        <v>0</v>
-      </c>
-      <c r="J27" s="49">
+      <c r="H27" s="46"/>
+      <c r="I27" s="47">
+        <v>0</v>
+      </c>
+      <c r="J27" s="48">
         <f t="shared" ref="J27:J35" si="2">I27*H27</f>
         <v>0</v>
       </c>
-      <c r="K27" s="50">
+      <c r="K27" s="49">
         <f t="shared" ref="K27:K35" si="3">J27/0.8475</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="52"/>
-      <c r="C28" s="53">
-        <v>0</v>
-      </c>
-      <c r="D28" s="54">
+      <c r="B28" s="51"/>
+      <c r="C28" s="52">
+        <v>0</v>
+      </c>
+      <c r="D28" s="53">
         <f t="shared" ref="D28:D36" si="4">C28*B28</f>
         <v>0</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="54">
         <f t="shared" ref="E28:E36" si="5">D28/0.8475</f>
         <v>0</v>
       </c>
-      <c r="G28" s="51"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="53">
-        <v>0</v>
-      </c>
-      <c r="J28" s="57">
+      <c r="G28" s="50"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="52">
+        <v>0</v>
+      </c>
+      <c r="J28" s="56">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K28" s="50">
+      <c r="K28" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="52"/>
-      <c r="C29" s="53">
-        <v>0</v>
-      </c>
-      <c r="D29" s="54">
+      <c r="B29" s="51"/>
+      <c r="C29" s="52">
+        <v>0</v>
+      </c>
+      <c r="D29" s="53">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E29" s="55">
+      <c r="E29" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G29" s="58"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="60">
-        <v>0</v>
-      </c>
-      <c r="J29" s="61">
+      <c r="G29" s="57"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="59">
+        <v>0</v>
+      </c>
+      <c r="J29" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K29" s="50">
+      <c r="K29" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="58" t="s">
+      <c r="A30" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="62">
-        <v>100000</v>
-      </c>
-      <c r="C30" s="60">
-        <v>0</v>
-      </c>
-      <c r="D30" s="63">
+      <c r="B30" s="61"/>
+      <c r="C30" s="59">
+        <v>0</v>
+      </c>
+      <c r="D30" s="62">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E30" s="55">
+      <c r="E30" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G30" s="58"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="60">
-        <v>0</v>
-      </c>
-      <c r="J30" s="61">
+      <c r="G30" s="57"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="59">
+        <v>0</v>
+      </c>
+      <c r="J30" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K30" s="50">
+      <c r="K30" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="62">
-        <v>50000</v>
-      </c>
-      <c r="C31" s="60">
-        <v>0</v>
-      </c>
-      <c r="D31" s="54">
+      <c r="B31" s="61"/>
+      <c r="C31" s="59">
+        <v>0</v>
+      </c>
+      <c r="D31" s="53">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E31" s="55">
+      <c r="E31" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G31" s="58"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="60">
-        <v>0</v>
-      </c>
-      <c r="J31" s="61">
+      <c r="G31" s="57"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="59">
+        <v>0</v>
+      </c>
+      <c r="J31" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K31" s="50">
+      <c r="K31" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="58" t="s">
+      <c r="A32" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="62">
-        <v>100000</v>
-      </c>
-      <c r="C32" s="60">
-        <v>0</v>
-      </c>
-      <c r="D32" s="54">
+      <c r="B32" s="61"/>
+      <c r="C32" s="59">
+        <v>0</v>
+      </c>
+      <c r="D32" s="53">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E32" s="55">
+      <c r="E32" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G32" s="64"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="12">
-        <v>0</v>
-      </c>
-      <c r="J32" s="13">
+      <c r="G32" s="63"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="11">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K32" s="50">
+      <c r="K32" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="67">
-        <v>50000</v>
-      </c>
-      <c r="C33" s="12">
-        <v>0</v>
-      </c>
-      <c r="D33" s="63">
+      <c r="B33" s="66"/>
+      <c r="C33" s="11">
+        <v>0</v>
+      </c>
+      <c r="D33" s="62">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E33" s="55">
+      <c r="E33" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G33" s="64"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="12">
-        <v>0</v>
-      </c>
-      <c r="J33" s="13">
+      <c r="G33" s="63"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="11">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K33" s="50">
+      <c r="K33" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="12">
-        <v>0</v>
-      </c>
-      <c r="D34" s="54">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="11">
+        <v>0</v>
+      </c>
+      <c r="D34" s="53">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E34" s="55">
+      <c r="E34" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G34" s="64"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="12">
-        <v>0</v>
-      </c>
-      <c r="J34" s="13">
+      <c r="G34" s="63"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="11">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K34" s="50">
+      <c r="K34" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="12">
-        <v>0</v>
-      </c>
-      <c r="D35" s="54">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="11">
+        <v>0</v>
+      </c>
+      <c r="D35" s="53">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E35" s="55">
+      <c r="E35" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G35" s="68"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="70">
-        <v>0</v>
-      </c>
-      <c r="J35" s="71">
+      <c r="G35" s="67"/>
+      <c r="H35" s="68"/>
+      <c r="I35" s="69">
+        <v>0</v>
+      </c>
+      <c r="J35" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K35" s="50">
+      <c r="K35" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="72"/>
-      <c r="B36" s="72"/>
-      <c r="C36" s="12">
-        <v>0</v>
-      </c>
-      <c r="D36" s="73">
+      <c r="A36" s="71"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="11">
+        <v>0</v>
+      </c>
+      <c r="D36" s="72">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E36" s="55">
+      <c r="E36" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G36" s="74" t="s">
+      <c r="G36" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="76">
+      <c r="H36" s="74"/>
+      <c r="I36" s="74"/>
+      <c r="J36" s="75">
         <f>SUM(J27:J35)</f>
         <v>0</v>
       </c>
-      <c r="K36" s="77">
+      <c r="K36" s="76">
         <f>SUM(K27:K35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="108" t="s">
+      <c r="A37" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="108"/>
-      <c r="C37" s="108"/>
-      <c r="D37" s="37">
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="36">
         <f>SUM(D23:D36)</f>
         <v>0</v>
       </c>
-      <c r="E37" s="78">
+      <c r="E37" s="77">
         <f>SUM(E28:E36)</f>
         <v>0</v>
       </c>
@@ -2189,468 +2181,467 @@
       <c r="A38" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="104"/>
-      <c r="C38" s="104"/>
-      <c r="D38" s="37">
+      <c r="B38" s="107"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="36">
         <f>D37*B38/100</f>
         <v>0</v>
       </c>
-      <c r="E38" s="79"/>
+      <c r="E38" s="78"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="109" t="s">
+      <c r="A39" s="108" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="109"/>
-      <c r="C39" s="109"/>
-      <c r="D39" s="42">
+      <c r="B39" s="108"/>
+      <c r="C39" s="108"/>
+      <c r="D39" s="41">
         <f>D37-D38</f>
         <v>0</v>
       </c>
-      <c r="E39" s="80">
+      <c r="E39" s="79">
         <f>D39/0.8475</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="103" t="s">
+      <c r="A42" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="B42" s="103"/>
-      <c r="C42" s="103"/>
-      <c r="D42" s="103"/>
-      <c r="E42" s="103"/>
-      <c r="F42" s="103"/>
+      <c r="B42" s="111"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="111"/>
+      <c r="E42" s="111"/>
+      <c r="F42" s="111"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="81" t="s">
+      <c r="A43" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="82">
-        <v>420000</v>
-      </c>
-      <c r="C43" s="83">
-        <v>0</v>
-      </c>
-      <c r="D43" s="84">
+      <c r="B43" s="81"/>
+      <c r="C43" s="82">
+        <v>0</v>
+      </c>
+      <c r="D43" s="83">
         <f>C43*B43</f>
         <v>0</v>
       </c>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
+      <c r="E43" s="82"/>
+      <c r="F43" s="82"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="82">
-        <v>80000</v>
-      </c>
-      <c r="C44" s="83">
-        <v>0</v>
-      </c>
-      <c r="D44" s="84">
+      <c r="B44" s="81"/>
+      <c r="C44" s="82">
+        <v>0</v>
+      </c>
+      <c r="D44" s="83">
         <f>C44*B44/0.8475</f>
         <v>0</v>
       </c>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="82">
-        <v>55000</v>
-      </c>
-      <c r="C45" s="83">
-        <v>0</v>
-      </c>
-      <c r="D45" s="84">
+      <c r="B45" s="81"/>
+      <c r="C45" s="82">
+        <v>0</v>
+      </c>
+      <c r="D45" s="83">
         <f>C45*B45/0.8475</f>
         <v>0</v>
       </c>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="82"/>
-      <c r="C46" s="83">
-        <v>0</v>
-      </c>
-      <c r="D46" s="84">
+      <c r="B46" s="81"/>
+      <c r="C46" s="82">
+        <v>0</v>
+      </c>
+      <c r="D46" s="83">
         <f>C46*B46/0.8475</f>
         <v>0</v>
       </c>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="82">
-        <v>100000</v>
-      </c>
-      <c r="C47" s="83">
-        <v>0</v>
-      </c>
-      <c r="D47" s="84">
+      <c r="B47" s="81"/>
+      <c r="C47" s="82">
+        <v>0</v>
+      </c>
+      <c r="D47" s="83">
         <f>C47*B47</f>
         <v>0</v>
       </c>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="82">
-        <v>100000</v>
-      </c>
-      <c r="C48" s="83">
-        <v>0</v>
-      </c>
-      <c r="D48" s="84">
+      <c r="B48" s="81"/>
+      <c r="C48" s="82">
+        <v>0</v>
+      </c>
+      <c r="D48" s="83">
         <f>C48*B48</f>
         <v>0</v>
       </c>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="82">
-        <v>100000</v>
-      </c>
-      <c r="C49" s="83">
-        <v>0</v>
-      </c>
-      <c r="D49" s="84">
+      <c r="B49" s="81"/>
+      <c r="C49" s="82">
+        <v>0</v>
+      </c>
+      <c r="D49" s="83">
         <f>C49*B49</f>
         <v>0</v>
       </c>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="85">
+      <c r="A50" s="11"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="82">
+        <v>0</v>
+      </c>
+      <c r="D50" s="84">
         <f>C50*B50</f>
         <v>0</v>
       </c>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="14"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="82">
+        <v>0</v>
+      </c>
+      <c r="D51" s="84">
+        <f>C51*B51</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B52" s="78"/>
-      <c r="C52" s="79"/>
-      <c r="D52" s="86">
+      <c r="B52" s="77"/>
+      <c r="C52" s="78"/>
+      <c r="D52" s="85">
         <f>SUM(D43:D51)</f>
         <v>0</v>
       </c>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="104">
-        <v>0</v>
-      </c>
-      <c r="C53" s="104"/>
-      <c r="D53" s="86">
+      <c r="B53" s="107">
+        <v>0</v>
+      </c>
+      <c r="C53" s="107"/>
+      <c r="D53" s="85">
         <f>D52*B53/100</f>
         <v>0</v>
       </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="105" t="s">
+      <c r="A54" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="105"/>
-      <c r="C54" s="105"/>
-      <c r="D54" s="106">
+      <c r="B54" s="112"/>
+      <c r="C54" s="112"/>
+      <c r="D54" s="113">
         <f>D52-D53</f>
         <v>0</v>
       </c>
-      <c r="E54" s="106"/>
-      <c r="F54" s="79"/>
+      <c r="E54" s="113"/>
+      <c r="F54" s="78"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="14"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
+      <c r="A55" s="13"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="102" t="s">
+      <c r="A58" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="102"/>
-      <c r="C58" s="102"/>
-      <c r="D58" s="102"/>
-      <c r="E58" s="102"/>
-      <c r="F58" s="102"/>
+      <c r="B58" s="110"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="110"/>
+      <c r="E58" s="110"/>
+      <c r="F58" s="110"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B59" s="87">
-        <v>200000</v>
-      </c>
-      <c r="C59" s="14">
-        <v>0</v>
-      </c>
-      <c r="D59" s="85">
+      <c r="B59" s="86"/>
+      <c r="C59" s="13">
+        <v>0</v>
+      </c>
+      <c r="D59" s="84">
         <f>C59*B59</f>
         <v>0</v>
       </c>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B60" s="87">
-        <v>100000</v>
-      </c>
-      <c r="C60" s="14">
-        <v>0</v>
-      </c>
-      <c r="D60" s="85">
+      <c r="B60" s="86"/>
+      <c r="C60" s="13">
+        <v>0</v>
+      </c>
+      <c r="D60" s="84">
         <f>C60*B60</f>
         <v>0</v>
       </c>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B61" s="87">
-        <v>100000</v>
-      </c>
-      <c r="C61" s="14">
-        <v>0</v>
-      </c>
-      <c r="D61" s="85">
+      <c r="B61" s="86"/>
+      <c r="C61" s="13">
+        <v>0</v>
+      </c>
+      <c r="D61" s="84">
         <f>C61*B61</f>
         <v>0</v>
       </c>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B62" s="87">
-        <v>50000</v>
-      </c>
-      <c r="C62" s="14"/>
-      <c r="D62" s="85">
+      <c r="B62" s="86"/>
+      <c r="C62" s="13">
+        <v>0</v>
+      </c>
+      <c r="D62" s="84">
         <f>C62*B62</f>
         <v>0</v>
       </c>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B63" s="87">
-        <v>30000</v>
-      </c>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14">
+      <c r="B63" s="86"/>
+      <c r="C63" s="13">
+        <v>0</v>
+      </c>
+      <c r="D63" s="84">
         <f>C63*B63</f>
         <v>0</v>
       </c>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="14"/>
-      <c r="B64" s="87"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
+      <c r="A64" s="13"/>
+      <c r="B64" s="86"/>
+      <c r="C64" s="13">
+        <v>0</v>
+      </c>
+      <c r="D64" s="84">
+        <f t="shared" ref="D64:D65" si="6">C64*B64</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="14"/>
-      <c r="B65" s="87"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
+      <c r="A65" s="13"/>
+      <c r="B65" s="86"/>
+      <c r="C65" s="13">
+        <v>0</v>
+      </c>
+      <c r="D65" s="84">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="102" t="s">
+      <c r="A66" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B66" s="102"/>
-      <c r="C66" s="102"/>
-      <c r="D66" s="88">
+      <c r="B66" s="110"/>
+      <c r="C66" s="110"/>
+      <c r="D66" s="87">
         <f>SUM(D59:D65)</f>
         <v>0</v>
       </c>
-      <c r="E66" s="89"/>
-      <c r="F66" s="89"/>
+      <c r="E66" s="88"/>
+      <c r="F66" s="88"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="90" t="s">
+      <c r="A70" s="89" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="91" t="s">
+      <c r="A71" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="B71" s="92" t="s">
+      <c r="B71" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="C71" s="93" t="s">
+      <c r="C71" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="D71" s="93" t="s">
+      <c r="D71" s="92" t="s">
         <v>55</v>
       </c>
-      <c r="E71" s="94" t="s">
+      <c r="E71" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="F71" s="94" t="s">
+      <c r="F71" s="93" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="95"/>
-      <c r="B72" s="96"/>
-      <c r="C72" s="66"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="67"/>
-      <c r="F72" s="97"/>
+      <c r="A72" s="94"/>
+      <c r="B72" s="95"/>
+      <c r="C72" s="65"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="66"/>
+      <c r="F72" s="96"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="95"/>
-      <c r="B73" s="96"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="67"/>
-      <c r="F73" s="97"/>
+      <c r="A73" s="94"/>
+      <c r="B73" s="95"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="66"/>
+      <c r="F73" s="96"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="95"/>
-      <c r="B74" s="96"/>
-      <c r="C74" s="66"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="67"/>
-      <c r="F74" s="97"/>
+      <c r="A74" s="94"/>
+      <c r="B74" s="95"/>
+      <c r="C74" s="65"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="66"/>
+      <c r="F74" s="96"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="95"/>
-      <c r="B75" s="98"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
+      <c r="A75" s="94"/>
+      <c r="B75" s="97"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="14"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
+      <c r="A76" s="13"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="14"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
+      <c r="A77" s="13"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="99" t="s">
+      <c r="A79" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="B79" s="99" t="s">
+      <c r="B79" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="C79" s="99" t="s">
+      <c r="C79" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="D79" s="99" t="s">
+      <c r="D79" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="E79" s="99" t="s">
+      <c r="E79" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="F79" s="99" t="s">
+      <c r="F79" s="98" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="12"/>
-      <c r="B80" s="66"/>
-      <c r="C80" s="100"/>
-      <c r="D80" s="101"/>
-      <c r="E80" s="101"/>
-      <c r="F80" s="101"/>
+      <c r="A80" s="11"/>
+      <c r="B80" s="65"/>
+      <c r="C80" s="99"/>
+      <c r="D80" s="100"/>
+      <c r="E80" s="100"/>
+      <c r="F80" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:L3"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="G25:K25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="D54:E54"/>
     <mergeCell ref="A58:F58"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup scale="35" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/server/templates/Template Excel Presupuesto.xlsx
+++ b/server/templates/Template Excel Presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w.pallero.gomez\Desktop\onyria-presupuestos\onyria-presupuestos\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3B1312-0F5E-466B-BA76-0A4AA7FD4727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560D1183-2109-46F7-90C2-7F6E803B6202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -932,6 +932,33 @@
     <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -942,33 +969,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1438,30 +1438,30 @@
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="4"/>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
+      <c r="A3" s="111" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="103" t="s">
+      <c r="G3" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -1482,8 +1482,7 @@
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="11">
-        <f>SUM(C28:C36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="12">
         <f>E39</f>
@@ -1510,8 +1509,7 @@
       </c>
       <c r="H5" s="19"/>
       <c r="I5" s="11">
-        <f>SUM(C43:C51)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="12">
         <f>D54</f>
@@ -1538,8 +1536,7 @@
       </c>
       <c r="H6" s="19"/>
       <c r="I6" s="11">
-        <f>SUM(C59:C65)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="12">
         <f>D66</f>
@@ -1566,8 +1563,7 @@
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="11">
-        <f>SUM(I27:I35)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="12">
         <f>K36*I7</f>
@@ -1594,8 +1590,7 @@
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="11">
-        <f>SUM(C5:C18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="12">
         <f>D21*I8</f>
@@ -1677,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="20"/>
-      <c r="G12" s="104" t="s">
+      <c r="G12" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="104"/>
+      <c r="H12" s="113"/>
       <c r="I12" s="27">
         <f>SUM(B13:I13)</f>
         <v>0</v>
@@ -1705,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="20"/>
-      <c r="G13" s="105" t="s">
+      <c r="G13" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="105"/>
+      <c r="H13" s="109"/>
       <c r="I13" s="29"/>
       <c r="J13" s="30"/>
     </row>
@@ -1725,10 +1720,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="20"/>
-      <c r="G14" s="105" t="s">
+      <c r="G14" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="105"/>
+      <c r="H14" s="109"/>
       <c r="I14" s="29"/>
       <c r="J14" s="31">
         <f>J15-J13</f>
@@ -1746,10 +1741,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="20"/>
-      <c r="G15" s="105" t="s">
+      <c r="G15" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="105"/>
+      <c r="H15" s="109"/>
       <c r="I15" s="29"/>
       <c r="J15" s="31">
         <f>J13*1.19</f>
@@ -1795,11 +1790,11 @@
       <c r="J18" s="35"/>
     </row>
     <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="106" t="s">
+      <c r="A19" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="106"/>
-      <c r="C19" s="106"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="107"/>
       <c r="D19" s="36">
         <f>SUM(D5:D18)</f>
         <v>0</v>
@@ -1814,8 +1809,8 @@
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="107"/>
-      <c r="C20" s="107"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="103"/>
       <c r="D20" s="36">
         <f>D19*B20/100</f>
         <v>0</v>
@@ -1838,22 +1833,22 @@
       <c r="J23" s="42"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G25" s="109" t="s">
+      <c r="G25" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="109"/>
-      <c r="I25" s="109"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="109"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="106"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="109" t="s">
+      <c r="A26" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="109"/>
-      <c r="C26" s="109"/>
-      <c r="D26" s="109"/>
-      <c r="E26" s="109"/>
+      <c r="B26" s="106"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
       <c r="G26" s="43" t="s">
         <v>2</v>
       </c>
@@ -2163,11 +2158,11 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="106" t="s">
+      <c r="A37" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="106"/>
-      <c r="C37" s="106"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="107"/>
       <c r="D37" s="36">
         <f>SUM(D23:D36)</f>
         <v>0</v>
@@ -2181,8 +2176,8 @@
       <c r="A38" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="107"/>
-      <c r="C38" s="107"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="103"/>
       <c r="D38" s="36">
         <f>D37*B38/100</f>
         <v>0</v>
@@ -2205,14 +2200,14 @@
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="111" t="s">
+      <c r="A42" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="B42" s="111"/>
-      <c r="C42" s="111"/>
-      <c r="D42" s="111"/>
-      <c r="E42" s="111"/>
-      <c r="F42" s="111"/>
+      <c r="B42" s="102"/>
+      <c r="C42" s="102"/>
+      <c r="D42" s="102"/>
+      <c r="E42" s="102"/>
+      <c r="F42" s="102"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="80" t="s">
@@ -2362,10 +2357,10 @@
       <c r="A53" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="107">
-        <v>0</v>
-      </c>
-      <c r="C53" s="107"/>
+      <c r="B53" s="103">
+        <v>0</v>
+      </c>
+      <c r="C53" s="103"/>
       <c r="D53" s="85">
         <f>D52*B53/100</f>
         <v>0</v>
@@ -2374,16 +2369,16 @@
       <c r="F53" s="13"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="112" t="s">
+      <c r="A54" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="112"/>
-      <c r="C54" s="112"/>
-      <c r="D54" s="113">
+      <c r="B54" s="104"/>
+      <c r="C54" s="104"/>
+      <c r="D54" s="105">
         <f>D52-D53</f>
         <v>0</v>
       </c>
-      <c r="E54" s="113"/>
+      <c r="E54" s="105"/>
       <c r="F54" s="78"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2395,14 +2390,14 @@
       <c r="F55" s="13"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="110" t="s">
+      <c r="A58" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="110"/>
-      <c r="C58" s="110"/>
-      <c r="D58" s="110"/>
-      <c r="E58" s="110"/>
-      <c r="F58" s="110"/>
+      <c r="B58" s="101"/>
+      <c r="C58" s="101"/>
+      <c r="D58" s="101"/>
+      <c r="E58" s="101"/>
+      <c r="F58" s="101"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
@@ -2506,11 +2501,11 @@
       <c r="F65" s="13"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="110" t="s">
+      <c r="A66" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="B66" s="110"/>
-      <c r="C66" s="110"/>
+      <c r="B66" s="101"/>
+      <c r="C66" s="101"/>
       <c r="D66" s="87">
         <f>SUM(D59:D65)</f>
         <v>0</v>
@@ -2621,27 +2616,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="D54:E54"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="G25:K25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:L3"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup scale="35" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
